--- a/EIBE_CS_SKU정보_드리미,압타밀,포티밀,화웨이,레이레이.xlsx
+++ b/EIBE_CS_SKU정보_드리미,압타밀,포티밀,화웨이,레이레이.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\지윤환\Desktop\DEVELOP_web\eibe_cs_mock_up\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C6B2A6-1AC6-491D-AE83-F2DE5B20262B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFB2783-D4B6-46E5-8650-64506DD24EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -457,7 +457,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -485,6 +485,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -551,10 +557,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -892,7 +898,7 @@
       <c r="D3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="12" t="s">
         <v>75</v>
       </c>
       <c r="F3" s="13" t="s">
@@ -909,7 +915,7 @@
       <c r="D4" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F4" s="13" t="s">
@@ -926,7 +932,7 @@
       <c r="D5" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="12" t="s">
         <v>77</v>
       </c>
       <c r="F5" s="13" t="s">
@@ -943,7 +949,7 @@
       <c r="D6" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="12" t="s">
         <v>78</v>
       </c>
       <c r="F6" s="13" t="s">
@@ -960,7 +966,7 @@
       <c r="D7" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="12" t="s">
         <v>79</v>
       </c>
       <c r="F7" s="13" t="s">
@@ -975,7 +981,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="11"/>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="12" t="s">
         <v>80</v>
       </c>
       <c r="F8" s="13" t="s">
@@ -990,7 +996,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="11"/>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="12" t="s">
         <v>81</v>
       </c>
       <c r="F9" s="13" t="s">
@@ -1005,7 +1011,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="11"/>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="12" t="s">
         <v>82</v>
       </c>
       <c r="F10" s="13" t="s">
@@ -1020,7 +1026,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="11"/>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F11" s="12" t="s">
@@ -1035,7 +1041,7 @@
         <v>12</v>
       </c>
       <c r="D12" s="11"/>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="12" t="s">
         <v>84</v>
       </c>
       <c r="F12" s="12" t="s">
@@ -1050,7 +1056,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="11"/>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="12" t="s">
         <v>85</v>
       </c>
       <c r="F13" s="12" t="s">
@@ -1065,7 +1071,7 @@
         <v>14</v>
       </c>
       <c r="D14" s="11"/>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="12" t="s">
         <v>86</v>
       </c>
       <c r="F14" s="12" t="s">
@@ -1080,7 +1086,7 @@
         <v>15</v>
       </c>
       <c r="D15" s="11"/>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="12" t="s">
         <v>88</v>
       </c>
       <c r="F15" s="12" t="s">
@@ -1095,7 +1101,7 @@
         <v>16</v>
       </c>
       <c r="D16" s="11"/>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="12" t="s">
         <v>87</v>
       </c>
       <c r="F16" s="12" t="s">
@@ -1110,7 +1116,7 @@
         <v>17</v>
       </c>
       <c r="D17" s="11"/>
-      <c r="E17" s="9"/>
+      <c r="E17" s="12"/>
       <c r="F17" s="12" t="s">
         <v>103</v>
       </c>
@@ -1123,7 +1129,7 @@
         <v>18</v>
       </c>
       <c r="D18" s="11"/>
-      <c r="E18" s="9"/>
+      <c r="E18" s="12"/>
       <c r="F18" s="12" t="s">
         <v>104</v>
       </c>
@@ -1136,7 +1142,7 @@
         <v>19</v>
       </c>
       <c r="D19" s="11"/>
-      <c r="E19" s="9"/>
+      <c r="E19" s="12"/>
       <c r="F19" s="13" t="s">
         <v>105</v>
       </c>
@@ -1149,7 +1155,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="11"/>
-      <c r="E20" s="9"/>
+      <c r="E20" s="12"/>
       <c r="F20" s="13" t="s">
         <v>106</v>
       </c>
@@ -1162,7 +1168,7 @@
         <v>21</v>
       </c>
       <c r="D21" s="11"/>
-      <c r="E21" s="9"/>
+      <c r="E21" s="12"/>
       <c r="F21" s="13" t="s">
         <v>107</v>
       </c>
@@ -1175,7 +1181,7 @@
         <v>22</v>
       </c>
       <c r="D22" s="11"/>
-      <c r="E22" s="9"/>
+      <c r="E22" s="12"/>
       <c r="F22" s="13" t="s">
         <v>108</v>
       </c>
@@ -1188,7 +1194,7 @@
         <v>23</v>
       </c>
       <c r="D23" s="11"/>
-      <c r="E23" s="9"/>
+      <c r="E23" s="12"/>
       <c r="F23" s="13" t="s">
         <v>109</v>
       </c>
